--- a/panchang-data/Mahameru2026.xlsx
+++ b/panchang-data/Mahameru2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5337">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16036,6 +16036,9 @@
   </si>
   <si>
     <t>121°04'48.93</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16525,7 +16528,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16611,7 +16614,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -16697,7 +16700,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16783,7 +16786,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -16869,7 +16872,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -16955,7 +16958,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -17041,7 +17044,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17127,7 +17130,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17213,7 +17216,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
@@ -17299,7 +17302,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17385,7 +17388,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17471,7 +17474,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17557,7 +17560,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>126</v>
@@ -17643,7 +17646,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17729,7 +17732,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17815,7 +17818,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
@@ -17901,7 +17904,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -17987,7 +17990,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18073,7 +18076,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18159,7 +18162,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -18245,7 +18248,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18331,7 +18334,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18417,7 +18420,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
@@ -18503,7 +18506,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18589,7 +18592,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18675,7 +18678,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18761,7 +18764,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
@@ -18847,7 +18850,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -18933,7 +18936,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19019,7 +19022,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>51</v>
@@ -19105,7 +19108,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19191,7 +19194,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19277,7 +19280,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19363,7 +19366,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>126</v>
@@ -19449,7 +19452,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19535,7 +19538,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19621,7 +19624,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -19707,7 +19710,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19793,7 +19796,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -19879,7 +19882,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -19965,7 +19968,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>126</v>
@@ -20051,7 +20054,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20137,7 +20140,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20223,7 +20226,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>51</v>
@@ -20309,7 +20312,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20395,7 +20398,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20481,7 +20484,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20567,7 +20570,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>126</v>
@@ -20653,7 +20656,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20739,7 +20742,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20825,7 +20828,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>51</v>
@@ -20911,7 +20914,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -20997,7 +21000,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21083,7 +21086,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21169,7 +21172,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>126</v>
@@ -21255,7 +21258,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21341,7 +21344,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21427,7 +21430,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>51</v>
@@ -21513,7 +21516,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21599,7 +21602,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21685,7 +21688,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21771,7 +21774,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>568</v>
+        <v>999</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>126</v>
@@ -21857,7 +21860,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -21943,7 +21946,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22029,7 +22032,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>51</v>
@@ -22115,7 +22118,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22201,7 +22204,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22287,7 +22290,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22373,7 +22376,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>126</v>
@@ -22459,7 +22462,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22545,7 +22548,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22631,7 +22634,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>51</v>
@@ -22717,7 +22720,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22803,7 +22806,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -22889,7 +22892,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -22975,7 +22978,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>126</v>
@@ -23061,7 +23064,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23147,7 +23150,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23233,7 +23236,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>51</v>
@@ -23319,7 +23322,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23405,7 +23408,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23491,7 +23494,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23577,7 +23580,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
@@ -23663,7 +23666,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23749,7 +23752,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23835,7 +23838,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>51</v>
@@ -23921,7 +23924,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24007,7 +24010,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24093,7 +24096,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24179,7 +24182,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>126</v>
@@ -24265,7 +24268,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>999</v>
+        <v>1425</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24351,7 +24354,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24437,7 +24440,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>51</v>
@@ -24523,7 +24526,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24609,7 +24612,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24695,7 +24698,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24781,7 +24784,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>126</v>
@@ -24867,7 +24870,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -24953,7 +24956,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25039,7 +25042,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>51</v>
@@ -25125,7 +25128,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25211,7 +25214,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25297,7 +25300,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25383,7 +25386,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>126</v>
@@ -25469,7 +25472,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25555,7 +25558,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25641,7 +25644,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>51</v>
@@ -25727,7 +25730,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25813,7 +25816,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -25899,7 +25902,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -25985,7 +25988,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>126</v>
@@ -26071,7 +26074,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26157,7 +26160,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26243,7 +26246,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>51</v>
@@ -26329,7 +26332,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26415,7 +26418,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26501,7 +26504,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26587,7 +26590,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>126</v>
@@ -26673,7 +26676,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -26759,7 +26762,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -26845,7 +26848,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1425</v>
+        <v>1862</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>51</v>
@@ -26931,7 +26934,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27017,7 +27020,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27103,7 +27106,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27189,7 +27192,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>126</v>
@@ -27275,7 +27278,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27361,7 +27364,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27447,7 +27450,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>51</v>
@@ -27533,7 +27536,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27619,7 +27622,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27705,7 +27708,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27791,7 +27794,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>126</v>
@@ -27877,7 +27880,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -27963,7 +27966,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28049,7 +28052,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
@@ -28135,7 +28138,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1862</v>
+        <v>2280</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28221,7 +28224,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28307,7 +28310,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28393,7 +28396,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>126</v>
@@ -28479,7 +28482,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28565,7 +28568,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28651,7 +28654,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>51</v>
@@ -28737,7 +28740,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28823,7 +28826,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -28909,7 +28912,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -28995,7 +28998,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>126</v>
@@ -29081,7 +29084,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29167,7 +29170,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29253,7 +29256,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>51</v>
@@ -29339,7 +29342,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29425,7 +29428,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1862</v>
+        <v>5336</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29511,7 +29514,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29597,7 +29600,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>126</v>
@@ -29683,7 +29686,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -29769,7 +29772,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -29855,7 +29858,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>51</v>
@@ -29941,7 +29944,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30027,7 +30030,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30113,7 +30116,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30199,7 +30202,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>126</v>
@@ -30285,7 +30288,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30371,7 +30374,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30457,7 +30460,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -30543,7 +30546,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30629,7 +30632,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2280</v>
+        <v>5336</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
